--- a/test_cases/gen_disturbance_profile.xlsx
+++ b/test_cases/gen_disturbance_profile.xlsx
@@ -2052,7 +2052,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">

--- a/test_cases/gen_disturbance_profile.xlsx
+++ b/test_cases/gen_disturbance_profile.xlsx
@@ -2052,7 +2052,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
